--- a/wtf-execl-transfrom/source/fight/output1.xlsx
+++ b/wtf-execl-transfrom/source/fight/output1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wtf\wtf-execl-transfrom\source\fight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bieren\taekwondo\WTF-Trans\WTF\wtf-execl-transfrom\source\fight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54B4111F-5BF3-479D-9ED9-C8235AF65098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDABBED6-D5B7-4D82-B9DD-1B152B1E4F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="3540" windowWidth="21600" windowHeight="11385" xr2:uid="{059B816E-B382-47CF-8510-32902495DA22}"/>
+    <workbookView xWindow="7300" yWindow="650" windowWidth="13150" windowHeight="15370" xr2:uid="{059B816E-B382-47CF-8510-32902495DA22}"/>
   </bookViews>
   <sheets>
     <sheet name="跆拳道test" sheetId="1" r:id="rId1"/>
@@ -2222,12 +2222,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N212"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="N52" s="1"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="N55" s="1"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="N58" s="1"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="N60" s="1"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="N61" s="1"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="N63" s="1"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>80</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>81</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>82</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>88</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>89</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>90</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>91</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>92</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>93</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>94</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>95</v>
       </c>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="N95" s="1"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>96</v>
       </c>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="N96" s="1"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>97</v>
       </c>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="N97" s="1"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>98</v>
       </c>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="N98" s="1"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>99</v>
       </c>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="N99" s="1"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>100</v>
       </c>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="N100" s="1"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>101</v>
       </c>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="N101" s="1"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>102</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>103</v>
       </c>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="N103" s="1"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>104</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>105</v>
       </c>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="N105" s="1"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>106</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>107</v>
       </c>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="N107" s="1"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>108</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>109</v>
       </c>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="N109" s="1"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>110</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>111</v>
       </c>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="N111" s="1"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>112</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>113</v>
       </c>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="N113" s="1"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>114</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>115</v>
       </c>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="N115" s="1"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>116</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>117</v>
       </c>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="N117" s="1"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>118</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>119</v>
       </c>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="N119" s="1"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>120</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>121</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>122</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>123</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>124</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>125</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>126</v>
       </c>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="N126" s="1"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>127</v>
       </c>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="N127" s="1"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>128</v>
       </c>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="N128" s="1"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>129</v>
       </c>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="N129" s="1"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>130</v>
       </c>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="N130" s="1"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>131</v>
       </c>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="N131" s="1"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>132</v>
       </c>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="N132" s="1"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>133</v>
       </c>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="N133" s="1"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>134</v>
       </c>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="N134" s="1"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>135</v>
       </c>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="N135" s="1"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>136</v>
       </c>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="N136" s="1"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>137</v>
       </c>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="N137" s="1"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>138</v>
       </c>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="N138" s="1"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>139</v>
       </c>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="N139" s="1"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>140</v>
       </c>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="N140" s="1"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>141</v>
       </c>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="N141" s="1"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>142</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>143</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>144</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>145</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>146</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>147</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>148</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>149</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>150</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>151</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>152</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>153</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>154</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>155</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>156</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>157</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>158</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>159</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>160</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>161</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>162</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>163</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>164</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>165</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>166</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>167</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>168</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>169</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>170</v>
       </c>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N170" s="1"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>171</v>
       </c>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="N171" s="1"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>172</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="N172" s="1"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>173</v>
       </c>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="N173" s="1"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>174</v>
       </c>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="N174" s="1"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>175</v>
       </c>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="N175" s="1"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>176</v>
       </c>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="N176" s="1"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>177</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>178</v>
       </c>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="N178" s="1"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>179</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>180</v>
       </c>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="N180" s="1"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>181</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>182</v>
       </c>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="N182" s="1"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>183</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>184</v>
       </c>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="N184" s="1"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>185</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>186</v>
       </c>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="N186" s="1"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>187</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>188</v>
       </c>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="N188" s="1"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>189</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>190</v>
       </c>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="N190" s="1"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>191</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>192</v>
       </c>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="N192" s="1"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>193</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>194</v>
       </c>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="N194" s="1"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>195</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>196</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>197</v>
       </c>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="N197" s="1"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>198</v>
       </c>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="N198" s="1"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>199</v>
       </c>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="N199" s="1"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>200</v>
       </c>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="N200" s="1"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>201</v>
       </c>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="N201" s="1"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>202</v>
       </c>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N202" s="1"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>203</v>
       </c>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="N203" s="1"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>204</v>
       </c>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="N204" s="1"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>205</v>
       </c>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="N205" s="1"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>206</v>
       </c>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N206" s="1"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>207</v>
       </c>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="N207" s="1"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>208</v>
       </c>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N208" s="1"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>209</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="N209" s="1"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>210</v>
       </c>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="N210" s="1"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>211</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>212</v>
       </c>
